--- a/documentos/tabla_tiempos.xlsx
+++ b/documentos/tabla_tiempos.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E32A5EF2-6670-437C-B225-73D56C87577A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{A6DC7CAF-B6F2-47AA-8155-7194B280C5C8}"/>
+    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{A6DC7CAF-B6F2-47AA-8155-7194B280C5C8}"/>
   </bookViews>
   <sheets>
     <sheet name="PDD" sheetId="1" r:id="rId1"/>
